--- a/data/GPS/Metricas_GPS - copia.xlsx
+++ b/data/GPS/Metricas_GPS - copia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C801EA20-609B-44AF-A76C-F20927ECAC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED82933B-87CB-4B60-BBC4-65BEA047C93E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -457,7 +457,7 @@
     <col min="6" max="7" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -504,7 +504,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>46271</v>
       </c>
@@ -518,28 +518,28 @@
         <v>19</v>
       </c>
       <c r="E2" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L2" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>
@@ -659,28 +659,28 @@
         <v>24</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M5" s="1">
         <v>0</v>
